--- a/Documentacion/Documentacion/TABLAS_BD_SAMGSDB.xlsx
+++ b/Documentacion/Documentacion/TABLAS_BD_SAMGSDB.xlsx
@@ -1,15 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo T14\OneDrive\Documentos\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20430" windowHeight="7440"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20430" windowHeight="7440" firstSheet="4" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="CAT_DEPARTAMENTO" sheetId="1" r:id="rId1"/>
@@ -17,6 +12,9 @@
     <sheet name="CATAL_PERFIL" sheetId="3" r:id="rId3"/>
     <sheet name="CONTROL_PASSW" sheetId="4" r:id="rId4"/>
     <sheet name="SYS_USU_SEGUIM" sheetId="5" r:id="rId5"/>
+    <sheet name="tbl_sistema_menus" sheetId="6" r:id="rId6"/>
+    <sheet name="tbl_sistema_AsignaPerfilesMenu" sheetId="7" r:id="rId7"/>
+    <sheet name="tbl_sistema_Usuarios" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="101">
   <si>
     <t>IDDEPTO</t>
   </si>
@@ -160,13 +158,184 @@
   </si>
   <si>
     <t>CONSULTAS</t>
+  </si>
+  <si>
+    <t>IMENUID</t>
+  </si>
+  <si>
+    <t>SDESCRIPCION</t>
+  </si>
+  <si>
+    <t>IPADREID</t>
+  </si>
+  <si>
+    <t>IPOSICION</t>
+  </si>
+  <si>
+    <t>SURL</t>
+  </si>
+  <si>
+    <t>DFECHACREACION</t>
+  </si>
+  <si>
+    <t>IUSERIDCREACION</t>
+  </si>
+  <si>
+    <t>DFECHAMOD</t>
+  </si>
+  <si>
+    <t>IUSUARIOIDMODIFICAION</t>
+  </si>
+  <si>
+    <t>FINACTIVO</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>~/Usuarios/index</t>
+  </si>
+  <si>
+    <t>08/02/2024 05:00:15.000000 PM</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>UTILERIAS</t>
+  </si>
+  <si>
+    <t>CATALOGO USUARIOS</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>CATALOGO DEPARTAMENTOS</t>
+  </si>
+  <si>
+    <t>~/departamentos/index</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>CATALOGO PERFILES</t>
+  </si>
+  <si>
+    <t>~/Perfiles/index</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>CATALOGO MENUS</t>
+  </si>
+  <si>
+    <t>~/Menus/index</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>ACCESOS</t>
+  </si>
+  <si>
+    <t>~/MenuAccesoPerfil/index</t>
+  </si>
+  <si>
+    <t>BPERMITEACCESO</t>
+  </si>
+  <si>
+    <t>BPERMITEMOD</t>
+  </si>
+  <si>
+    <t>BPERMITEDEL</t>
+  </si>
+  <si>
+    <t>UALTA</t>
+  </si>
+  <si>
+    <t>08/02/2024 05:13:23.000000 PM</t>
+  </si>
+  <si>
+    <t>VCHIDUSERCORP</t>
+  </si>
+  <si>
+    <t>SUSERNAME</t>
+  </si>
+  <si>
+    <t>SPASWORD</t>
+  </si>
+  <si>
+    <t>SPREGUNTASECRETA</t>
+  </si>
+  <si>
+    <t>SRESPUESTASECRETA</t>
+  </si>
+  <si>
+    <t>BACTIVO</t>
+  </si>
+  <si>
+    <t>FCAMBIOPASS</t>
+  </si>
+  <si>
+    <t>ICADUCIDAD</t>
+  </si>
+  <si>
+    <t>BINACTIVO</t>
+  </si>
+  <si>
+    <t>FMODIFICACION</t>
+  </si>
+  <si>
+    <t>FBAJA</t>
+  </si>
+  <si>
+    <t>JABO</t>
+  </si>
+  <si>
+    <t>J@BO1234</t>
+  </si>
+  <si>
+    <t>CUAL ES MI EDAD</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>09/03/2024 05:22:24.000000 PM</t>
+  </si>
+  <si>
+    <t>08/02/2024 05:22:24.000000 PM</t>
+  </si>
+  <si>
+    <t>JOSE</t>
+  </si>
+  <si>
+    <t>J@se1234</t>
+  </si>
+  <si>
+    <t>LUGAR DE NACIMIENTO</t>
+  </si>
+  <si>
+    <t>MEXICO</t>
+  </si>
+  <si>
+    <t>09/03/2024 05:23:07.000000 PM</t>
+  </si>
+  <si>
+    <t>08/02/2024 05:23:07.000000 PM</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -182,13 +351,25 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="22"/>
+        <bgColor indexed="9"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="4">
@@ -248,7 +429,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -278,6 +459,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -287,7 +469,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -560,7 +743,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -569,22 +752,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="52.85546875" customWidth="1"/>
+    <col min="1" max="1" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.81640625" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
     </row>
     <row r="2" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
@@ -598,25 +781,25 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="14"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C4" s="11"/>
+    </row>
+    <row r="5" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2</v>
       </c>
       <c r="B5" t="s">
         <v>40</v>
       </c>
-      <c r="C5" s="14"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C5" s="11"/>
+    </row>
+    <row r="16" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="B16" s="7"/>
     </row>
   </sheetData>
@@ -631,42 +814,42 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:O4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.5703125" customWidth="1"/>
-    <col min="6" max="6" width="33.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.5703125" customWidth="1"/>
-    <col min="9" max="9" width="17.28515625" customWidth="1"/>
-    <col min="10" max="10" width="31.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.140625" customWidth="1"/>
+    <col min="1" max="1" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.54296875" customWidth="1"/>
+    <col min="6" max="6" width="33.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.54296875" customWidth="1"/>
+    <col min="9" max="9" width="17.26953125" customWidth="1"/>
+    <col min="10" max="10" width="31.7265625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.81640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
-      <c r="L1" s="12"/>
-      <c r="M1" s="12"/>
-      <c r="N1" s="12"/>
-      <c r="O1" s="12"/>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+    </row>
+    <row r="2" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -724,7 +907,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>32</v>
       </c>
@@ -755,7 +938,7 @@
       <c r="J4" t="s">
         <v>38</v>
       </c>
-      <c r="K4" s="14">
+      <c r="K4" s="11">
         <v>45329</v>
       </c>
     </row>
@@ -770,21 +953,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" customWidth="1"/>
-    <col min="2" max="2" width="45.5703125" customWidth="1"/>
+    <col min="1" max="1" width="12.54296875" customWidth="1"/>
+    <col min="2" max="2" width="45.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
     </row>
     <row r="2" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -795,7 +978,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
@@ -803,7 +986,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2</v>
       </c>
@@ -811,7 +994,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>3</v>
       </c>
@@ -830,21 +1013,21 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="24.42578125" customWidth="1"/>
-    <col min="3" max="3" width="22.140625" customWidth="1"/>
+    <col min="2" max="2" width="24.453125" customWidth="1"/>
+    <col min="3" max="3" width="22.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
@@ -868,27 +1051,27 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="7" max="7" width="14.85546875" customWidth="1"/>
-    <col min="8" max="8" width="13.85546875" customWidth="1"/>
-    <col min="9" max="9" width="40.85546875" customWidth="1"/>
+    <col min="7" max="7" width="14.81640625" customWidth="1"/>
+    <col min="8" max="8" width="13.81640625" customWidth="1"/>
+    <col min="9" max="9" width="40.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
@@ -925,4 +1108,982 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A1" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="G1" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="H1" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="I1" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="J1" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="K1" s="15" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A2" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="D2" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="F2" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="G2" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="K2" s="16"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="F3" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="G3" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="H3" s="16"/>
+      <c r="I3" s="16"/>
+      <c r="J3" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="K3" s="16"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="H4" s="16"/>
+      <c r="I4" s="16"/>
+      <c r="J4" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="K4" s="16"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="H5" s="16"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="K5" s="16"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A6" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="K6" s="16"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A7" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="H7" s="16"/>
+      <c r="I7" s="16"/>
+      <c r="J7" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="K7" s="16"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A8" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="H8" s="16"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="K8" s="16"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H22"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="F1" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="H1" s="15" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="D2" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="G2" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2" s="16" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="F3" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="G3" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="H3" s="16" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="H4" s="16" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="H5" s="16" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="H6" s="16" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="H7" s="16" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="H8" s="16" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="H9" s="16" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="G10" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="H10" s="16" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="H11" s="16" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="G12" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="H12" s="16" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="G13" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="H13" s="16" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E14" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="G14" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="H14" s="16" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E15" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="F15" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="G15" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="H15" s="16" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A16" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="G16" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="H16" s="16" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A17" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="D17" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="E17" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="F17" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="G17" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="H17" s="16" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A18" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="E18" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="F18" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="G18" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="H18" s="16" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A19" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="D19" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="E19" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="F19" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="G19" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="H19" s="16" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A20" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="E20" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="F20" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="H20" s="16" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A21" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="E21" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="F21" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="G21" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="H21" s="16" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A22" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="E22" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="F22" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="G22" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="H22" s="16" t="s">
+        <v>77</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:P3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A1" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="H1" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="I1" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="J1" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="K1" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="L1" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="M1" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="N1" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="O1" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="P1" s="15" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A2" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="D2" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="G2" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="H2" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="I2" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="J2" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="K2" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L2" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="M2" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="N2" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="O2" s="16"/>
+      <c r="P2" s="16"/>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="F3" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="G3" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="I3" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="J3" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="K3" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L3" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="M3" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="N3" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="O3" s="16"/>
+      <c r="P3" s="16"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>